--- a/data/observaciones.xlsx
+++ b/data/observaciones.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\walte\OneDrive\Documentos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos-js\InfraVial\backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="102">
   <si>
     <t/>
   </si>
@@ -206,48 +206,6 @@
     <t>idObsSH</t>
   </si>
   <si>
-    <t>obstrucción de señalización vertical por vegetación existente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">acumulación de basura en la ubicación del paral </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización vertical no cumple con la altura del paral </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización vertical mal ubicada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de tablero de señalización vertical caída </t>
-  </si>
-  <si>
-    <t xml:space="preserve">inexistencia de señalización vertical a nivel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización vertical bandalizada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización vertical reciclada </t>
-  </si>
-  <si>
-    <t xml:space="preserve">obstrucción de señalización vertical por invasión del espacio publico </t>
-  </si>
-  <si>
-    <t xml:space="preserve">inexistencia de señalización vertical </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización no reglamentarias </t>
-  </si>
-  <si>
-    <t xml:space="preserve">el tablero no cumple con las dimensiones según el tipo de señal </t>
-  </si>
-  <si>
-    <t xml:space="preserve">existencia de señalización no acorde con el perfil vial </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ubicación de la señal no acorde con el sentido del perfil vial </t>
-  </si>
-  <si>
     <t>txtObs</t>
   </si>
   <si>
@@ -255,13 +213,139 @@
   </si>
   <si>
     <t>id mongodb</t>
+  </si>
+  <si>
+    <t>Alta tasa de accidentalidad</t>
+  </si>
+  <si>
+    <t>Altura libre obstruida por cableado de servicios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contaminacion por acumulacion de basuras o escombros </t>
+  </si>
+  <si>
+    <t>cuneta en mal estado de conservacion</t>
+  </si>
+  <si>
+    <t>Disminusion de la infraestructura de estacionamiento</t>
+  </si>
+  <si>
+    <t>Disminusion de la infraestructura vial</t>
+  </si>
+  <si>
+    <t>Exceso de acompañanates o pasajeros en vehiculos automotores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">existencia de puente vehicular en el tramo vial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">existencia de seañalizacion no acorde con el perfil vial </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existencia de tapas de alcantarillado y rejillas de desague a desnivel del perfil vial </t>
+  </si>
+  <si>
+    <t>Falta de arborización con especies nativas</t>
+  </si>
+  <si>
+    <t>Falta de conciencia en la población sobre temas de seguridad vial</t>
+  </si>
+  <si>
+    <t>Falta de control a la contaminación sonora</t>
+  </si>
+  <si>
+    <t>Falta de manejo de agua de escorrentias</t>
+  </si>
+  <si>
+    <t>Falta de poda en la vegetación existente</t>
+  </si>
+  <si>
+    <t>Inestabilidad de terreno a lado y lado de la vía</t>
+  </si>
+  <si>
+    <t>Inexactitud o falta de ubicación, dimensiones y materiales de las señales en edificios para accesibilidad a las personas al medio fisico</t>
+  </si>
+  <si>
+    <t>inexistencia de bombeo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inexistencia de tapas de alcantarillado y rejillas de desague </t>
+  </si>
+  <si>
+    <t xml:space="preserve">inexistencia de uniformidad de andenes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inexistencia o falta de contrahuellas, huellas,tramos rectos,descansos, pasamanos y vados de las personas al medio fisico </t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de estacionamientos accesibles a las personas al medio fisico</t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de infraestructura para la accesibilidad (vias de circulación peatonales u horizontales)</t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de paraderos accesibles para transporte publico colectivo y otros</t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de señales de orientacion (croquis planos modelos)</t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de señales direccionales y funcionales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inexistencia o falta de señales visuales y tactiles </t>
+  </si>
+  <si>
+    <t>Inexistencia o falta de señalización horizontal y vertical para la accesibilidad de las personas al medio fisico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invación del espacio público </t>
+  </si>
+  <si>
+    <t xml:space="preserve">invasion del espacio destinado a cicloruta </t>
+  </si>
+  <si>
+    <t>Limpieza de andenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No uso de elementos de proteccion personal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se evidencia ampliación de la vía sin ningún tipo de supervisión o señalizacion vertical temporal </t>
+  </si>
+  <si>
+    <t xml:space="preserve">se evidencia señalizacion vertical bandalizada </t>
+  </si>
+  <si>
+    <t>se evidencia señalizacion vertical recicladas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se visualiza una fluencia de agua por uno de los costados de la via </t>
+  </si>
+  <si>
+    <t>taponamiento de la red pluvial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uniformidad de perfil vial </t>
+  </si>
+  <si>
+    <t>Uso excesivo de vehiculos particulares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violación a las señales de transito por parte de la población </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -302,6 +386,19 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -409,11 +506,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -457,14 +555,15 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Hoja1" xfId="1"/>
+    <cellStyle name="Normal_OBS VIAS TRAMOS" xfId="4"/>
     <cellStyle name="Normal_observacionesSH" xfId="3"/>
     <cellStyle name="Normal_observacionesSV" xfId="2"/>
   </cellStyles>
@@ -1975,134 +2074,344 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="80.85546875" customWidth="1"/>
+    <col min="2" max="2" width="80.85546875" style="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" t="s">
-        <v>73</v>
+        <v>60</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>72</v>
-      </c>
     </row>
     <row r="16" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <sortState ref="B1:B15">
